--- a/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
+++ b/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzxxc\Documents\deep_lerning\venv\AIQuant-3rd-project\06_코드\qa\manual_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138FB721-E125-44E9-AC13-81ED057CAB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EA2F55-D50F-41B8-82BD-A33EB6B24CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1148,13 +1148,13 @@
     <t>K</t>
   </si>
   <si>
-    <t>04-13 조정 전 수익률</t>
+    <t>04-13 조정 전 수익률 (%)</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>04-13 조정 후 수익률</t>
+    <t>04-13 조정 후 수익률 (%)</t>
   </si>
   <si>
     <t>엑셀 = 코드 일치 항목 수</t>
@@ -1167,12 +1167,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0.0"/>
     <numFmt numFmtId="177" formatCode="0.000000"/>
     <numFmt numFmtId="178" formatCode="0.0000"/>
     <numFmt numFmtId="179" formatCode="0.00000000"/>
     <numFmt numFmtId="180" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="181" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1320,7 +1321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1362,20 +1363,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1721,98 +1716,98 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="50"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
@@ -1885,86 +1880,86 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="48"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
@@ -2122,52 +2117,52 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>338</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="3"/>
@@ -2224,15 +2219,15 @@
       <c r="B11" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="31">
         <f>'12 계산 P10'!B15</f>
         <v>315154781.22222221</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32">
+      <c r="D11" s="32"/>
+      <c r="E11" s="33">
         <v>315154781.22222221</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>C11-E11</f>
         <v>0</v>
       </c>
@@ -2253,11 +2248,11 @@
         <f>90</f>
         <v>90</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="35">
+      <c r="D12" s="35"/>
+      <c r="E12" s="36">
         <v>90</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>C12-E12</f>
         <v>0</v>
       </c>
@@ -2274,15 +2269,15 @@
       <c r="B13" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="31">
         <f>'12 계산 P10'!B11</f>
         <v>316884754.03555554</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32">
+      <c r="D13" s="32"/>
+      <c r="E13" s="33">
         <v>316884754.0355556</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>C13-E13</f>
         <v>0</v>
       </c>
@@ -2327,11 +2322,11 @@
         <f>'12 계산 P10'!B18</f>
         <v>1</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35">
+      <c r="D15" s="35"/>
+      <c r="E15" s="36">
         <v>1</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f t="shared" ref="F15:F21" si="0">C15-E15</f>
         <v>0</v>
       </c>
@@ -2352,11 +2347,11 @@
         <f>'12 계산 P10'!B19</f>
         <v>11</v>
       </c>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35">
+      <c r="D16" s="35"/>
+      <c r="E16" s="36">
         <v>11</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2377,11 +2372,11 @@
         <f>'21 계산 비중'!C19</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37">
+      <c r="D17" s="37"/>
+      <c r="E17" s="38">
         <v>1</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2398,15 +2393,15 @@
       <c r="B18" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="18">
         <f>'21 계산 비중'!D39</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39">
+      <c r="D18" s="37"/>
+      <c r="E18" s="38">
         <v>16.666666666666661</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2423,15 +2418,15 @@
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="31">
         <f>'22 계산 지수'!D29</f>
         <v>1023.8015667579472</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42">
+      <c r="D19" s="32"/>
+      <c r="E19" s="33">
         <v>1023.8015667579469</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2448,15 +2443,15 @@
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C20" s="26">
-        <f>'30 계산 분할'!D23</f>
-        <v>-0.77258883248730958</v>
-      </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="44">
-        <v>-0.77258883248730958</v>
-      </c>
-      <c r="F20" s="33">
+      <c r="C20" s="18">
+        <f>'30 계산 분할'!D23*100</f>
+        <v>-77.258883248730953</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38">
+        <v>-77.258883248730953</v>
+      </c>
+      <c r="F20" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2473,15 +2468,15 @@
       <c r="B21" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="C21" s="26">
-        <f>'30 계산 분할'!D24</f>
-        <v>0.13705583756345185</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="44">
-        <v>0.13705583756345191</v>
-      </c>
-      <c r="F21" s="33">
+      <c r="C21" s="18">
+        <f>'30 계산 분할'!D24*100</f>
+        <v>13.705583756345185</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="38">
+        <v>13.705583756345179</v>
+      </c>
+      <c r="F21" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2495,7 +2490,7 @@
       <c r="B23" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="C23" s="45">
+      <c r="C23" s="39">
         <f>COUNTIF(G10:G21,"일치")</f>
         <v>12</v>
       </c>
@@ -2538,90 +2533,90 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="50"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="3"/>
@@ -3151,30 +3146,30 @@
       <c r="G35" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="52"/>
+      <c r="B37" s="46"/>
       <c r="C37" s="7" t="str">
         <f>INDEX($B$14:$B$35,MATCH(5,$F$14:$F$35,0))</f>
         <v>2026-06-23</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="52"/>
+      <c r="B38" s="46"/>
       <c r="C38" s="6">
         <f>SUM($E$14:$E$35)</f>
         <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="52"/>
+      <c r="B39" s="46"/>
       <c r="C39" s="6">
         <f>COUNTA($B$14:$B$35)-SUM($E$14:$E$35)</f>
         <v>2</v>
@@ -3184,48 +3179,48 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="46" t="s">
+      <c r="A44" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3287,51 +3282,51 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="53" t="s">
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="53" t="s">
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="53" t="s">
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="53" t="s">
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="53" t="s">
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="53" t="s">
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="53" t="s">
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="53" t="s">
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
@@ -10869,64 +10864,64 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="3"/>
@@ -11216,52 +11211,52 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -11302,28 +11297,28 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
@@ -11462,12 +11457,12 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
@@ -11482,36 +11477,36 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11980,72 +11975,72 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="50"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3"/>
@@ -12563,80 +12558,80 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>297</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="50"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3"/>
@@ -13185,11 +13180,11 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="45" t="s">
         <v>304</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="52"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="46"/>
       <c r="D29" s="24">
         <f>H27*1000</f>
         <v>1023.8015667579472</v>
@@ -13233,79 +13228,79 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="40" t="s">
         <v>308</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="50"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="40" t="s">
         <v>309</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="40" t="s">
         <v>310</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="3"/>
@@ -13557,11 +13552,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="45" t="s">
         <v>317</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="46"/>
       <c r="D23" s="27">
         <f>G18</f>
         <v>-0.77258883248730958</v>
@@ -13571,11 +13566,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="45" t="s">
         <v>319</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="52"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="46"/>
       <c r="D24" s="27">
         <f>F18</f>
         <v>0.13705583756345185</v>
@@ -13585,22 +13580,22 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="45" t="s">
         <v>321</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="52"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="26">
         <f>D23-D24</f>
         <v>-0.90964467005076144</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="52"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="46"/>
       <c r="D26" s="26">
         <f>D25*VLOOKUP("010120",'21 계산 비중'!$B$22:$D$36,3,FALSE)</f>
         <v>-5.0535815002820075E-2</v>
@@ -13610,163 +13605,163 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="50"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="40" t="s">
         <v>329</v>
       </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="50"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
+      <c r="A36" s="44"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="46" t="s">
+      <c r="A37" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="46" t="s">
+      <c r="A39" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="50"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="46" t="s">
+      <c r="A41" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
+++ b/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzxxc\Documents\deep_lerning\venv\AIQuant-3rd-project\06_코드\qa\manual_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EA2F55-D50F-41B8-82BD-A33EB6B24CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420972D3-CAFC-4C3C-8E33-B8FE2319B134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="396">
   <si>
     <t>J-5 엑셀 수식 교차검산본</t>
   </si>
@@ -1085,82 +1085,151 @@
     <t>엑셀−코드</t>
   </si>
   <si>
+    <t>수기−코드</t>
+  </si>
+  <si>
     <t>판정</t>
   </si>
   <si>
+    <t>가져올 곳</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
     <t>자료마감일</t>
   </si>
   <si>
+    <t>02 시트 B26</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>KTOS ADTV90 (USD)</t>
   </si>
   <si>
+    <t>03-04 시트 B108</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
     <t>ADTV90 분모 (개장일수)</t>
   </si>
   <si>
+    <t>03-04 시트 B104</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
     <t>미국 P10 하한 (USD)</t>
   </si>
   <si>
+    <t>05 시트 B32</t>
+  </si>
+  <si>
     <t>E</t>
   </si>
   <si>
     <t>제외</t>
   </si>
   <si>
+    <t>05 시트 B33</t>
+  </si>
+  <si>
     <t>F</t>
   </si>
   <si>
+    <t>05 시트 B35</t>
+  </si>
+  <si>
     <t>G</t>
   </si>
   <si>
     <t>2종목 이상 탈락 최소 n</t>
   </si>
   <si>
+    <t>05 시트 B43</t>
+  </si>
+  <si>
     <t>H</t>
   </si>
   <si>
     <t>목표비중 합계</t>
   </si>
   <si>
+    <t>06 시트 E26</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
     <t>최대 비중 (%)</t>
   </si>
   <si>
+    <t>06 시트 B53</t>
+  </si>
+  <si>
     <t>J</t>
   </si>
   <si>
     <t>2026-04-07 지수 레벨</t>
   </si>
   <si>
+    <t>07 시트 D36</t>
+  </si>
+  <si>
     <t>K</t>
   </si>
   <si>
     <t>04-13 조정 전 수익률 (%)</t>
   </si>
   <si>
+    <t>08 시트 C27</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
     <t>04-13 조정 후 수익률 (%)</t>
   </si>
   <si>
-    <t>엑셀 = 코드 일치 항목 수</t>
+    <t>08 시트 C28</t>
+  </si>
+  <si>
+    <t>엑셀 = 코드 (참고용 · 자동 계산)</t>
   </si>
   <si>
     <t>/ 12</t>
+  </si>
+  <si>
+    <t>★ 3자 일치 — 수기 검산 결과</t>
+  </si>
+  <si>
+    <t>수기 미기입</t>
+  </si>
+  <si>
+    <t>차이 발생</t>
+  </si>
+  <si>
+    <t>■ D열(수기값)이 비어 있으면 검산은 끝나지 않은 것입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  엑셀과 코드가 일치하는 것은 '같은 규칙을 두 환경에서 돌려 같은 값이 나왔다'는 뜻일 뿐입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  둘 다 제가 같은 룰북 해석으로 만든 것이라, 해석이 틀렸다면 사이좋게 같이 틀립니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  사람이 손으로 따라가 D열을 채워야 그 가능성이 걸러집니다. 그것이 J-5 수기 검산입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  순서: ① J5_수기검산_워크시트.xlsx 를 손으로 채운다  ② 저장한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ③ I열 '가져올 곳'을 보고 D열에 옮겨 적는다  ④ H열 판정을 확인한다</t>
   </si>
 </sst>
 </file>
@@ -2096,27 +2165,29 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="5" width="22" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="44" t="s">
         <v>338</v>
       </c>
@@ -2128,7 +2199,7 @@
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="40" t="s">
         <v>339</v>
       </c>
@@ -2140,7 +2211,7 @@
       <c r="G5" s="41"/>
       <c r="H5" s="41"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="40" t="s">
         <v>340</v>
       </c>
@@ -2152,7 +2223,7 @@
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="40" t="s">
         <v>341</v>
       </c>
@@ -2164,7 +2235,7 @@
       <c r="G7" s="41"/>
       <c r="H7" s="41"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>342</v>
@@ -2185,15 +2256,21 @@
         <v>347</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C10" s="16" t="str">
         <f>'05 계산 자료마감일'!C37</f>
@@ -2206,18 +2283,24 @@
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="13" t="str">
-        <f>IF(C10=E10,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="13" t="str">
+        <f>IF(D10="","수기 미기입",IF(AND(C10=E10,D10=E10),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C11" s="31">
         <f>'12 계산 P10'!B15</f>
@@ -2231,18 +2314,25 @@
         <f>C11-E11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="13" t="str">
-        <f>IF(ABS(C11-E11)&lt;0.000001,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G11" s="34" t="str">
+        <f>IF(D11="","",D11-E11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="13" t="str">
+        <f>IF(D11="","수기 미기입",IF(AND(ABS(C11-E11)&lt;0.000001,ABS(D11-E11)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C12" s="11">
         <f>90</f>
@@ -2256,18 +2346,25 @@
         <f>C12-E12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="13" t="str">
-        <f>IF(ABS(C12-E12)&lt;0.000001,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G12" s="34" t="str">
+        <f>IF(D12="","",D12-E12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="13" t="str">
+        <f>IF(D12="","수기 미기입",IF(AND(ABS(C12-E12)&lt;0.000001,ABS(D12-E12)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C13" s="31">
         <f>'12 계산 P10'!B11</f>
@@ -2281,15 +2378,22 @@
         <f>C13-E13</f>
         <v>0</v>
       </c>
-      <c r="G13" s="13" t="str">
-        <f>IF(ABS(C13-E13)&lt;0.000001,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G13" s="34" t="str">
+        <f>IF(D13="","",D13-E13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="13" t="str">
+        <f>IF(D13="","수기 미기입",IF(AND(ABS(C13-E13)&lt;0.000001,ABS(D13-E13)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>235</v>
@@ -2300,20 +2404,26 @@
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="30" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="13" t="str">
-        <f>IF(C14=E14,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="13" t="str">
+        <f>IF(D14="","수기 미기입",IF(AND(C14=E14,D14=E14),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>238</v>
@@ -2330,18 +2440,25 @@
         <f t="shared" ref="F15:F21" si="0">C15-E15</f>
         <v>0</v>
       </c>
-      <c r="G15" s="13" t="str">
-        <f t="shared" ref="G15:G21" si="1">IF(ABS(C15-E15)&lt;0.000001,"일치","★차이★")</f>
-        <v>일치</v>
-      </c>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G15" s="34" t="str">
+        <f t="shared" ref="G15:G21" si="1">IF(D15="","",D15-E15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="13" t="str">
+        <f t="shared" ref="H15:H21" si="2">IF(D15="","수기 미기입",IF(AND(ABS(C15-E15)&lt;0.000001,ABS(D15-E15)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C16" s="11">
         <f>'12 계산 P10'!B19</f>
@@ -2355,18 +2472,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="13" t="str">
+      <c r="G16" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+        <v/>
+      </c>
+      <c r="H16" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C17" s="18">
         <f>'21 계산 비중'!C19</f>
@@ -2380,18 +2504,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="13" t="str">
+      <c r="G17" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+        <v/>
+      </c>
+      <c r="H17" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C18" s="18">
         <f>'21 계산 비중'!D39</f>
@@ -2405,18 +2536,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="13" t="str">
+      <c r="G18" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+        <v/>
+      </c>
+      <c r="H18" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C19" s="31">
         <f>'22 계산 지수'!D29</f>
@@ -2430,18 +2568,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="13" t="str">
+      <c r="G19" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+        <v/>
+      </c>
+      <c r="H19" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C20" s="18">
         <f>'30 계산 분할'!D23*100</f>
@@ -2455,18 +2600,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="13" t="str">
+      <c r="G20" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+        <v/>
+      </c>
+      <c r="H20" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C21" s="18">
         <f>'30 계산 분할'!D24*100</f>
@@ -2480,30 +2632,176 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="13" t="str">
+      <c r="G21" s="34" t="str">
         <f t="shared" si="1"/>
-        <v>일치</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B23" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="C23" s="39">
-        <f>COUNTIF(G10:G21,"일치")</f>
+        <v/>
+      </c>
+      <c r="H21" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>수기 미기입</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B23" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C23" s="11">
+        <f>SUMPRODUCT(--(TEXT(C10:C21,"0.000000")=TEXT(E10:E21,"0.000000")))</f>
         <v>12</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>372</v>
-      </c>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B24" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="39">
+        <f>COUNTIF(H10:H21,"3자 일치")</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B25" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C25" s="11">
+        <f>COUNTIF(H10:H21,"수기 미기입")</f>
+        <v>12</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B26" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C26" s="11">
+        <f>COUNTIF(H10:H21,"★차이★")</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A29" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" s="42"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A33" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A34" s="43" t="s">
+        <v>395</v>
+      </c>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="11">
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A30:J30"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
+++ b/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzxxc\Documents\deep_lerning\venv\AIQuant-3rd-project\06_코드\qa\manual_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5A2CC8-635F-43FC-89A4-38A6FA9F49F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F40C1BB-D678-46E2-A0A2-E898A361A3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="408">
   <si>
     <t>J-5 엑셀 수식 교차검산본</t>
   </si>
@@ -683,7 +683,10 @@
     <t xml:space="preserve">  거래대금 합계 = SUMPRODUCT(종가열, 거래량열)     ← 제59조 재구성. 빈 칸은 0으로 처리됨</t>
   </si>
   <si>
-    <t xml:space="preserve">  ADTV90        = 합계 ÷ 90                        ← 분모는 관측창 길이 90 (결측 없음)</t>
+    <t xml:space="preserve">  분모          = 90 − 결측일수                     ← 룰북 §8.1 R6. 정지·무거래는 분모에 남는다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ADTV90        = 합계 ÷ 분모</t>
   </si>
   <si>
     <t xml:space="preserve">  시즈닝        = IF(유효관측일수 &gt;= 90, "SEASONED", "INCOMPLETE")</t>
@@ -693,6 +696,12 @@
   </si>
   <si>
     <t>유효관측일수</t>
+  </si>
+  <si>
+    <t>결측일수</t>
+  </si>
+  <si>
+    <t>분모</t>
   </si>
   <si>
     <t>거래대금 합계</t>
@@ -2209,17 +2218,17 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="45" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
@@ -2231,7 +2240,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -2243,7 +2252,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -2255,7 +2264,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="41" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -2268,28 +2277,28 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>87</v>
@@ -2297,10 +2306,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C10" s="18" t="str">
         <f>'05 계산 자료마감일'!C46</f>
@@ -2321,16 +2330,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C11" s="32">
         <f>'12 계산 P10'!B15</f>
@@ -2353,16 +2362,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C12" s="13">
         <f>90</f>
@@ -2385,16 +2394,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="8" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C13" s="32">
         <f>'12 계산 P10'!B11</f>
@@ -2417,16 +2426,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C14" s="18" t="str">
         <f>'12 계산 P10'!B16</f>
@@ -2434,7 +2443,7 @@
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="31" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>16</v>
@@ -2447,16 +2456,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C15" s="13">
         <f>'12 계산 P10'!B18</f>
@@ -2479,16 +2488,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="8" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C16" s="13">
         <f>'12 계산 P10'!B19</f>
@@ -2511,16 +2520,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C17" s="20">
         <f>'21 계산 비중'!C19</f>
@@ -2543,16 +2552,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C18" s="20">
         <f>'21 계산 비중'!D39</f>
@@ -2575,16 +2584,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="8" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C19" s="32">
         <f>'22 계산 지수'!D29</f>
@@ -2607,16 +2616,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="8" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C20" s="20">
         <f>'30 계산 분할'!D23*100</f>
@@ -2639,16 +2648,16 @@
         <v>수기 미기입</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C21" s="20">
         <f>'30 계산 분할'!D24*100</f>
@@ -2671,61 +2680,61 @@
         <v>수기 미기입</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J21" s="4"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B23" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C23" s="13">
         <f>SUMPRODUCT(--(TEXT(C10:C21,"0.000000")=TEXT(E10:E21,"0.000000")))</f>
         <v>12</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B24" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C24" s="40">
         <f>COUNTIF(H10:H21,"3자 일치")</f>
         <v>0</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B25" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C25" s="13">
         <f>COUNTIF(H10:H21,"수기 미기입")</f>
         <v>12</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B26" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C26" s="13">
         <f>COUNTIF(H10:H21,"★차이★")</f>
         <v>0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="43" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -2739,7 +2748,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="44" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -2753,7 +2762,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="44" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -2767,7 +2776,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="44" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="42"/>
@@ -2793,7 +2802,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="44" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
@@ -2807,7 +2816,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="44" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
@@ -11251,29 +11260,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="45" t="s">
         <v>79</v>
       </c>
@@ -11285,7 +11296,7 @@
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
         <v>211</v>
       </c>
@@ -11297,7 +11308,7 @@
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
         <v>212</v>
       </c>
@@ -11309,7 +11320,7 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="41" t="s">
         <v>213</v>
       </c>
@@ -11321,7 +11332,7 @@
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="41" t="s">
         <v>214</v>
       </c>
@@ -11333,308 +11344,386 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="8">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C12" s="13">
         <f>COUNTIF('10 원자료 US거래'!D5:D94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D12" s="13">
+        <f>COUNTIF('10 원자료 US거래'!D5:D94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <f t="shared" ref="E12:E20" si="0">90-D12</f>
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!B5:B94,'10 원자료 US거래'!C5:C94)</f>
         <v>112708926244</v>
       </c>
-      <c r="E11" s="14">
-        <f t="shared" ref="E11:E19" si="0">D11/90</f>
+      <c r="G12" s="14">
+        <f t="shared" ref="G12:G20" si="1">F12/E12</f>
         <v>1252321402.7111111</v>
       </c>
-      <c r="F11" s="15" t="str">
-        <f t="shared" ref="F11:F19" si="1">IF(C11&gt;=90,"SEASONED","INCOMPLETE")</f>
+      <c r="H12" s="15" t="str">
+        <f t="shared" ref="H12:H20" si="2">IF(C12&gt;=90,"SEASONED","INCOMPLETE")</f>
         <v>SEASONED</v>
       </c>
-      <c r="G11" s="14">
-        <f t="shared" ref="G11:G19" si="2">IF(F11="SEASONED",E11,"")</f>
+      <c r="I12" s="14">
+        <f t="shared" ref="I12:I20" si="3">IF(H12="SEASONED",G12,"")</f>
         <v>1252321402.7111111</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="8">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="8">
         <v>2</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C13" s="13">
         <f>COUNTIF('10 원자료 US거래'!G5:G94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D13" s="13">
+        <f>COUNTIF('10 원자료 US거래'!G5:G94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!E5:E94,'10 원자료 US거래'!F5:F94)</f>
         <v>118273833381</v>
       </c>
-      <c r="E12" s="14">
-        <f t="shared" si="0"/>
+      <c r="G13" s="14">
+        <f t="shared" si="1"/>
         <v>1314153704.2333333</v>
       </c>
-      <c r="F12" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H13" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G12" s="14">
-        <f t="shared" si="2"/>
+      <c r="I13" s="14">
+        <f t="shared" si="3"/>
         <v>1314153704.2333333</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="8">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="8">
         <v>3</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C14" s="13">
         <f>COUNTIF('10 원자료 US거래'!J5:J94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D14" s="13">
+        <f>COUNTIF('10 원자료 US거래'!J5:J94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!H5:H94,'10 원자료 US거래'!I5:I94)</f>
         <v>120842745197</v>
       </c>
-      <c r="E13" s="14">
-        <f t="shared" si="0"/>
+      <c r="G14" s="14">
+        <f t="shared" si="1"/>
         <v>1342697168.8555555</v>
       </c>
-      <c r="F13" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H14" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G13" s="14">
-        <f t="shared" si="2"/>
+      <c r="I14" s="14">
+        <f t="shared" si="3"/>
         <v>1342697168.8555555</v>
       </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="8">
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="8">
         <v>4</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C15" s="13">
         <f>COUNTIF('10 원자료 US거래'!M5:M94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D15" s="13">
+        <f>COUNTIF('10 원자료 US거래'!M5:M94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!K5:K94,'10 원자료 US거래'!L5:L94)</f>
         <v>28586355386</v>
       </c>
-      <c r="E14" s="14">
-        <f t="shared" si="0"/>
+      <c r="G15" s="14">
+        <f t="shared" si="1"/>
         <v>317626170.95555556</v>
       </c>
-      <c r="F14" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H15" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G14" s="14">
-        <f t="shared" si="2"/>
+      <c r="I15" s="14">
+        <f t="shared" si="3"/>
         <v>317626170.95555556</v>
       </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="8">
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="8">
         <v>5</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C16" s="13">
         <f>COUNTIF('10 원자료 US거래'!P5:P94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D16" s="13">
+        <f>COUNTIF('10 원자료 US거래'!P5:P94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!N5:N94,'10 원자료 US거래'!O5:O94)</f>
         <v>91472793949</v>
       </c>
-      <c r="E15" s="14">
-        <f t="shared" si="0"/>
+      <c r="G16" s="14">
+        <f t="shared" si="1"/>
         <v>1016364377.2111111</v>
       </c>
-      <c r="F15" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H16" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G15" s="14">
-        <f t="shared" si="2"/>
+      <c r="I16" s="14">
+        <f t="shared" si="3"/>
         <v>1016364377.2111111</v>
       </c>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="8">
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" s="8">
         <v>6</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C17" s="13">
         <f>COUNTIF('10 원자료 US거래'!S5:S94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D17" s="13">
+        <f>COUNTIF('10 원자료 US거래'!S5:S94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!Q5:Q94,'10 원자료 US거래'!R5:R94)</f>
         <v>225774322948.48001</v>
       </c>
-      <c r="E16" s="14">
-        <f t="shared" si="0"/>
+      <c r="G17" s="14">
+        <f t="shared" si="1"/>
         <v>2508603588.3164444</v>
       </c>
-      <c r="F16" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H17" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G16" s="14">
-        <f t="shared" si="2"/>
+      <c r="I17" s="14">
+        <f t="shared" si="3"/>
         <v>2508603588.3164444</v>
       </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" s="8">
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" s="8">
         <v>7</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C18" s="13">
         <f>COUNTIF('10 원자료 US거래'!V5:V94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D18" s="13">
+        <f>COUNTIF('10 원자료 US거래'!V5:V94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!T5:T94,'10 원자료 US거래'!U5:U94)</f>
         <v>28363930310</v>
       </c>
-      <c r="E17" s="14">
-        <f t="shared" si="0"/>
+      <c r="G18" s="14">
+        <f t="shared" si="1"/>
         <v>315154781.22222221</v>
       </c>
-      <c r="F17" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H18" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G17" s="14">
-        <f t="shared" si="2"/>
+      <c r="I18" s="14">
+        <f t="shared" si="3"/>
         <v>315154781.22222221</v>
       </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18" s="8">
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" s="8">
         <v>8</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C19" s="13">
         <f>COUNTIF('10 원자료 US거래'!Y5:Y94,"TRADED")</f>
         <v>90</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D19" s="13">
+        <f>COUNTIF('10 원자료 US거래'!Y5:Y94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!W5:W94,'10 원자료 US거래'!X5:X94)</f>
         <v>119016426077</v>
       </c>
-      <c r="E18" s="14">
-        <f t="shared" si="0"/>
+      <c r="G19" s="14">
+        <f t="shared" si="1"/>
         <v>1322404734.1888888</v>
       </c>
-      <c r="F18" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H19" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>SEASONED</v>
       </c>
-      <c r="G18" s="14">
-        <f t="shared" si="2"/>
+      <c r="I19" s="14">
+        <f t="shared" si="3"/>
         <v>1322404734.1888888</v>
       </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="8">
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="8">
         <v>9</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C20" s="13">
         <f>COUNTIF('10 원자료 US거래'!AB5:AB94,"TRADED")</f>
         <v>7</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D20" s="13">
+        <f>COUNTIF('10 원자료 US거래'!AB5:AB94,"DATA_MISSING")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="13">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
         <f>SUMPRODUCT('10 원자료 US거래'!Z5:Z94,'10 원자료 US거래'!AA5:AA94)</f>
         <v>313722960645</v>
       </c>
-      <c r="E19" s="14">
-        <f t="shared" si="0"/>
+      <c r="G20" s="14">
+        <f t="shared" si="1"/>
         <v>3485810673.8333335</v>
       </c>
-      <c r="F19" s="15" t="str">
-        <f t="shared" si="1"/>
+      <c r="H20" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>INCOMPLETE</v>
       </c>
-      <c r="G19" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="I20" s="14" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="41" t="s">
-        <v>223</v>
+      <c r="J20" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
@@ -11644,9 +11733,9 @@
       <c r="G22" s="42"/>
       <c r="H22" s="42"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
@@ -11656,9 +11745,9 @@
       <c r="G23" s="42"/>
       <c r="H23" s="42"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="42"/>
@@ -11668,11 +11757,24 @@
       <c r="G24" s="42"/>
       <c r="H24" s="42"/>
     </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
@@ -11698,17 +11800,17 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="45" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
@@ -11716,7 +11818,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -11724,7 +11826,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -11732,109 +11834,109 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B9" s="13">
-        <f>COUNT('11 계산 ADTV90'!G11:G19)</f>
+        <f>COUNT('11 계산 ADTV90'!I12:I20)</f>
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B10" s="16">
         <f>(B9-1)*0.1</f>
         <v>0.70000000000000007</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B11" s="17">
-        <f>PERCENTILE('11 계산 ADTV90'!G11:G19,0.1)</f>
+        <f>PERCENTILE('11 계산 ADTV90'!I12:I20,0.1)</f>
         <v>316884754.03555554</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B12" s="14">
-        <f>SMALL('11 계산 ADTV90'!G11:G19,1)</f>
+        <f>SMALL('11 계산 ADTV90'!I12:I20,1)</f>
         <v>315154781.22222221</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B13" s="14">
-        <f>SMALL('11 계산 ADTV90'!G11:G19,2)</f>
+        <f>SMALL('11 계산 ADTV90'!I12:I20,2)</f>
         <v>317626170.95555556</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B14" s="14">
         <f>B12+(B10-INT(B10))*(B13-B12)</f>
         <v>316884754.03555554</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B15" s="14">
-        <f>INDEX('11 계산 ADTV90'!E11:E19,MATCH("KTOS",'11 계산 ADTV90'!B11:B19,0))</f>
+        <f>INDEX('11 계산 ADTV90'!G12:G20,MATCH("KTOS",'11 계산 ADTV90'!B12:B20,0))</f>
         <v>315154781.22222221</v>
       </c>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B16" s="18" t="str">
         <f>IF(B15&gt;=B11,"편입","제외")</f>
         <v>제외</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B17" s="16">
         <f>(B15/B11-1)*100</f>
@@ -11844,31 +11946,31 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B18" s="13">
-        <f>COUNTIF('11 계산 ADTV90'!G11:G19,"&lt;"&amp;B11)</f>
+        <f>COUNTIF('11 계산 ADTV90'!I12:I20,"&lt;"&amp;B11)</f>
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B19" s="13">
         <f>CEILING(1/0.1,1)+1</f>
         <v>11</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="45" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
@@ -11876,19 +11978,19 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B23" s="14">
-        <f>PERCENTILE('11 계산 ADTV90'!E11:E19,0.1)</f>
+        <f>PERCENTILE('11 계산 ADTV90'!G12:G20,0.1)</f>
         <v>317131893.0088889</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="45" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
@@ -11896,7 +11998,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="41" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
@@ -11904,7 +12006,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="41" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -11912,7 +12014,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="41" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -11949,12 +12051,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -11965,12 +12067,12 @@
         <v>69</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>168</v>
@@ -11981,7 +12083,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>171</v>
@@ -11993,22 +12095,22 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -12016,16 +12118,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F9" s="11">
         <v>794000</v>
@@ -12039,16 +12141,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F10" s="11">
         <v>1333000</v>
@@ -12062,16 +12164,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F11" s="11">
         <v>188800</v>
@@ -12085,16 +12187,16 @@
         <v>4</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F12" s="11">
         <v>59500</v>
@@ -12108,16 +12210,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F13" s="11">
         <v>794000</v>
@@ -12131,16 +12233,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F14" s="11">
         <v>902000</v>
@@ -12154,16 +12256,16 @@
         <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F15" s="11">
         <v>2653000</v>
@@ -12177,16 +12279,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F16" s="11">
         <v>391000</v>
@@ -12203,13 +12305,13 @@
         <v>121</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F17" s="11">
         <v>106.33</v>
@@ -12226,13 +12328,13 @@
         <v>122</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F18" s="11">
         <v>124.85</v>
@@ -12249,13 +12351,13 @@
         <v>123</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F19" s="11">
         <v>127.7</v>
@@ -12272,13 +12374,13 @@
         <v>125</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F20" s="11">
         <v>365.56</v>
@@ -12295,13 +12397,13 @@
         <v>126</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F21" s="11">
         <v>894.78</v>
@@ -12318,13 +12420,13 @@
         <v>127</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F22" s="11">
         <v>67.7</v>
@@ -12341,13 +12443,13 @@
         <v>128</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F23" s="11">
         <v>312.2</v>
@@ -12376,12 +12478,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -12396,7 +12498,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -12406,7 +12508,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -12416,7 +12518,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="41" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -12434,7 +12536,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="41" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -12444,7 +12546,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="41" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -12455,16 +12557,16 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>87</v>
@@ -12475,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C13" s="20">
         <f t="shared" ref="C13:C18" si="0">1/6</f>
@@ -12496,7 +12598,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C14" s="20">
         <f t="shared" si="0"/>
@@ -12517,7 +12619,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C15" s="20">
         <f t="shared" si="0"/>
@@ -12538,7 +12640,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C16" s="20">
         <f t="shared" si="0"/>
@@ -12559,7 +12661,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C17" s="20">
         <f t="shared" si="0"/>
@@ -12580,7 +12682,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C18" s="20">
         <f t="shared" si="0"/>
@@ -12598,7 +12700,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B19" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C19" s="21">
         <f>SUM(C13:C18)</f>
@@ -12609,19 +12711,19 @@
         <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
@@ -12900,7 +13002,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D37" s="21">
         <f>SUM(D22:D36)</f>
@@ -12909,7 +13011,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B39" s="21">
         <f>MAX(D22:D36)</f>
@@ -12924,7 +13026,7 @@
         <v>16.666666666666664</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -12959,12 +13061,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -12982,7 +13084,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -12995,7 +13097,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -13008,7 +13110,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="41" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -13032,7 +13134,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="41" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -13046,25 +13148,25 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>87</v>
@@ -13582,7 +13684,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="G27" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H27" s="24">
         <f>SUM(H12:H26)</f>
@@ -13591,7 +13693,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="46" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B29" s="49"/>
       <c r="C29" s="47"/>
@@ -13629,12 +13731,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="23" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -13650,7 +13752,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
@@ -13661,7 +13763,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -13681,7 +13783,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="41" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -13692,7 +13794,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="41" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
@@ -13703,7 +13805,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="41" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -13718,19 +13820,19 @@
         <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -13790,7 +13892,7 @@
         <v>788000</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E15" s="26">
         <f t="shared" si="0"/>
@@ -13816,7 +13918,7 @@
         <v>788000</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E16" s="26">
         <f t="shared" si="0"/>
@@ -13842,7 +13944,7 @@
         <v>788000</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E17" s="26">
         <f t="shared" si="0"/>
@@ -13963,7 +14065,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="46" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="47"/>
@@ -13972,12 +14074,12 @@
         <v>-0.77258883248730958</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="46" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B24" s="49"/>
       <c r="C24" s="47"/>
@@ -13986,12 +14088,12 @@
         <v>0.13705583756345185</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="46" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B25" s="49"/>
       <c r="C25" s="47"/>
@@ -14002,7 +14104,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="46" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B26" s="49"/>
       <c r="C26" s="47"/>
@@ -14011,12 +14113,12 @@
         <v>-5.0535815002820075E-2</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="43" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -14027,7 +14129,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="44" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -14038,7 +14140,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="44" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
@@ -14049,7 +14151,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="45" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -14069,7 +14171,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="41" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
@@ -14080,7 +14182,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="41" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -14100,7 +14202,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="41" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B37" s="42"/>
       <c r="C37" s="42"/>
@@ -14111,7 +14213,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="41" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
@@ -14122,7 +14224,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="41" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
@@ -14142,7 +14244,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="41" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B41" s="42"/>
       <c r="C41" s="42"/>
@@ -14153,7 +14255,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="42"/>
@@ -14164,7 +14266,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="41" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>

--- a/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
+++ b/06_코드/qa/manual_check/J5_엑셀수식_교차검산.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzxxc\Documents\deep_lerning\venv\AIQuant-3rd-project\06_코드\qa\manual_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F40C1BB-D678-46E2-A0A2-E898A361A3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C16C352-3B2C-48C6-A296-44B70F7640EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="409">
   <si>
     <t>J-5 엑셀 수식 교차검산본</t>
   </si>
@@ -1248,6 +1248,9 @@
   </si>
   <si>
     <t>차이 발생</t>
+  </si>
+  <si>
+    <t>입력 고쳐야 함 (형식·단위)</t>
   </si>
   <si>
     <t>■ D열(수기값)이 비어 있으면 검산은 끝나지 않은 것입니다.</t>
@@ -2204,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2326,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="15" t="str">
-        <f>IF(D10="","수기 미기입",IF(AND(C10=E10,D10=E10),"3자 일치","★차이★"))</f>
+        <f>IF(D10="","수기 미기입",IF(AND(C10=E10,OR(TRIM(D10)&amp;""=E10&amp;"",TEXT(D10,"yyyy-mm-dd")=E10&amp;"")),"3자 일치","★차이★"))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I10" s="4" t="s">
@@ -2354,11 +2357,11 @@
         <v>0</v>
       </c>
       <c r="G11" s="35" t="str">
-        <f>IF(D11="","",D11-E11)</f>
+        <f>IF(D11="","",IF(ISERROR(D11*1),"형식오류",D11*1-E11))</f>
         <v/>
       </c>
       <c r="H11" s="15" t="str">
-        <f>IF(D11="","수기 미기입",IF(AND(ABS(C11-E11)&lt;0.000001,ABS(D11-E11)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <f>IF(D11="","수기 미기입",IF(ISERROR(D11*1),"★형식오류 — 숫자만 입력★",IF(AND(ABS(C11-E11)&lt;0.000001,ABS(D11*1-E11)&lt;0.000001),"3자 일치",IF(ABS(D11*100-E11)&lt;0.000001,"★단위오류 — %를 빼고 입력★","★차이★"))))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2386,11 +2389,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="35" t="str">
-        <f>IF(D12="","",D12-E12)</f>
+        <f>IF(D12="","",IF(ISERROR(D12*1),"형식오류",D12*1-E12))</f>
         <v/>
       </c>
       <c r="H12" s="15" t="str">
-        <f>IF(D12="","수기 미기입",IF(AND(ABS(C12-E12)&lt;0.000001,ABS(D12-E12)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <f>IF(D12="","수기 미기입",IF(ISERROR(D12*1),"★형식오류 — 숫자만 입력★",IF(AND(ABS(C12-E12)&lt;0.000001,ABS(D12*1-E12)&lt;0.000001),"3자 일치",IF(ABS(D12*100-E12)&lt;0.000001,"★단위오류 — %를 빼고 입력★","★차이★"))))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I12" s="4" t="s">
@@ -2418,11 +2421,11 @@
         <v>0</v>
       </c>
       <c r="G13" s="35" t="str">
-        <f>IF(D13="","",D13-E13)</f>
+        <f>IF(D13="","",IF(ISERROR(D13*1),"형식오류",D13*1-E13))</f>
         <v/>
       </c>
       <c r="H13" s="15" t="str">
-        <f>IF(D13="","수기 미기입",IF(AND(ABS(C13-E13)&lt;0.000001,ABS(D13-E13)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <f>IF(D13="","수기 미기입",IF(ISERROR(D13*1),"★형식오류 — 숫자만 입력★",IF(AND(ABS(C13-E13)&lt;0.000001,ABS(D13*1-E13)&lt;0.000001),"3자 일치",IF(ABS(D13*100-E13)&lt;0.000001,"★단위오류 — %를 빼고 입력★","★차이★"))))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I13" s="4" t="s">
@@ -2452,7 +2455,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="15" t="str">
-        <f>IF(D14="","수기 미기입",IF(AND(C14=E14,D14=E14),"3자 일치","★차이★"))</f>
+        <f>IF(D14="","수기 미기입",IF(AND(C14=E14,OR(TRIM(D14)&amp;""=E14&amp;"",TEXT(D14,"yyyy-mm-dd")=E14&amp;"")),"3자 일치","★차이★"))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I14" s="4" t="s">
@@ -2480,11 +2483,11 @@
         <v>0</v>
       </c>
       <c r="G15" s="35" t="str">
-        <f t="shared" ref="G15:G21" si="1">IF(D15="","",D15-E15)</f>
+        <f t="shared" ref="G15:G21" si="1">IF(D15="","",IF(ISERROR(D15*1),"형식오류",D15*1-E15))</f>
         <v/>
       </c>
       <c r="H15" s="15" t="str">
-        <f t="shared" ref="H15:H21" si="2">IF(D15="","수기 미기입",IF(AND(ABS(C15-E15)&lt;0.000001,ABS(D15-E15)&lt;0.000001),"3자 일치","★차이★"))</f>
+        <f t="shared" ref="H15:H21" si="2">IF(D15="","수기 미기입",IF(ISERROR(D15*1),"★형식오류 — 숫자만 입력★",IF(AND(ABS(C15-E15)&lt;0.000001,ABS(D15*1-E15)&lt;0.000001),"3자 일치",IF(ABS(D15*100-E15)&lt;0.000001,"★단위오류 — %를 빼고 입력★","★차이★"))))</f>
         <v>수기 미기입</v>
       </c>
       <c r="I15" s="4" t="s">
@@ -2732,22 +2735,20 @@
         <v>398</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A28" s="43" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B27" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
+      <c r="C27" s="13">
+        <f>COUNTIF(H10:H21,"★형식오류*")+COUNTIF(H10:H21,"★단위오류*")</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="43" t="s">
         <v>403</v>
       </c>
       <c r="B29" s="42"/>
@@ -2789,7 +2790,9 @@
       <c r="J31" s="42"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A32" s="43"/>
+      <c r="A32" s="44" t="s">
+        <v>406</v>
+      </c>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
@@ -2801,9 +2804,7 @@
       <c r="J32" s="42"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A33" s="44" t="s">
-        <v>406</v>
-      </c>
+      <c r="A33" s="43"/>
       <c r="B33" s="42"/>
       <c r="C33" s="42"/>
       <c r="D33" s="42"/>
@@ -2828,12 +2829,26 @@
       <c r="I34" s="42"/>
       <c r="J34" s="42"/>
     </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A35" s="44" t="s">
+        <v>408</v>
+      </c>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A4:H4"/>
